--- a/jira_export_2026-10-21.xlsx
+++ b/jira_export_2026-10-21.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>45,921 €</t>
+          <t>46,010 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>15,125 €</t>
+          <t>15,215 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>388 h</t>
+          <t>390 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2101,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
@@ -2116,11 +2116,11 @@
       <c r="N19" s="12" t="n">
         <v>895</v>
       </c>
-      <c r="O19" s="16" t="n">
-        <v>805.5</v>
+      <c r="O19" s="12" t="n">
+        <v>895</v>
       </c>
       <c r="P19" s="12" t="n">
-        <v>537</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="20">
@@ -2245,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
@@ -2758,27 +2758,27 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)] - Réinstallation nouveaux serveurs (test et prod)</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>API Publication</t>
+          <t>Réinstallation nouveaux serveurs (test et prod)</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2805,57 +2805,57 @@
         <v>1</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="O29" s="16" t="n">
-        <v>179</v>
+        <v>0</v>
+      </c>
+      <c r="O29" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>119.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+          <t>API Publication</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2865,69 +2865,69 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>1068.45</v>
-      </c>
-      <c r="O30" s="15" t="n">
-        <v>3331.05</v>
+        <v>200</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>179</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>666.21</v>
+        <v>119.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfert de compétence Analyse </t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -2949,37 +2949,37 @@
         <v>1</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>455</v>
-      </c>
-      <c r="O31" s="16" t="n">
-        <v>136.5</v>
+        <v>1068.45</v>
+      </c>
+      <c r="O31" s="12" t="n">
+        <v>3331.05</v>
       </c>
       <c r="P31" s="12" t="n">
-        <v>60.67</v>
+        <v>666.21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35445</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BOURG EN BRESSE] - Mise à jour carto LIEXP SAAS</t>
+          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOURG EN BRESSE</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Mise à jour carto LIEXP SAAS</t>
+          <t xml:space="preserve">Transfert de compétence Analyse </t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
@@ -3014,51 +3014,59 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L32" s="14" t="inlineStr"/>
-      <c r="M32" s="14" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L32" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="M32" s="14" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
       <c r="N32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="15" t="n">
-        <v>0</v>
+        <v>455</v>
+      </c>
+      <c r="O32" s="16" t="n">
+        <v>136.5</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35445</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[CD 92] - Modélisation suite audit sur site</t>
+          <t>[COMMUNE DE BOURG EN BRESSE] - Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>COMMUNE DE BOURG EN BRESSE</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Modélisation suite audit sur site</t>
+          <t>Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3068,7 +3076,7 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -3085,57 +3093,49 @@
         <v>1</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L33" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35439</t>
-        </is>
-      </c>
-      <c r="M33" s="11" t="inlineStr">
-        <is>
-          <t>00180506</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L33" s="11" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr"/>
       <c r="N33" s="12" t="n">
-        <v>703.398</v>
-      </c>
-      <c r="O33" s="16" t="n">
-        <v>437.14</v>
+        <v>0</v>
+      </c>
+      <c r="O33" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P33" s="12" t="n">
-        <v>72.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
+          <t>[CD 92] - Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>GeODP - Migration V2 (presta)</t>
+          <t>Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3145,64 +3145,64 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>5783.002</v>
-      </c>
-      <c r="O34" s="15" t="n">
-        <v>5783.002</v>
+        <v>703.398</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>437.14</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>0</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35313</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
+          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAREOULT</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Migration Geodp Placier</t>
+          <t>GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3222,64 +3222,64 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35319</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00179389</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1053</v>
-      </c>
-      <c r="O35" s="16" t="n">
-        <v>1040</v>
+        <v>5783.002</v>
+      </c>
+      <c r="O35" s="12" t="n">
+        <v>5783.002</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>346.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35295</t>
+          <t>PDMDEP-35313</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)] - MM - Up - LiExp - Pastell (iParapheur)</t>
+          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>COMMUNE DE GAREOULT</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Pastell (iParapheur)</t>
+          <t>Migration Geodp Placier</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
@@ -3301,101 +3301,109 @@
         <v>2</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35301</t>
+          <t>PDMDEP-35319</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00179371</t>
+          <t>00179389</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="15" t="n">
-        <v>230</v>
+        <v>1053</v>
+      </c>
+      <c r="O36" s="16" t="n">
+        <v>1040</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>230</v>
+        <v>346.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35261</t>
+          <t>PDMDEP-35295</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
+          <t>[CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)] - MM - Up - LiExp - Pastell (iParapheur)</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Reprise des données TLPE</t>
+          <t>MM - Up - LiExp - Pastell (iParapheur)</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L37" s="11" t="inlineStr"/>
-      <c r="M37" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35301</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>00179371</t>
+        </is>
+      </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35261</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -3405,12 +3413,12 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>Reprise des données TLPE</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3420,39 +3428,31 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35212</t>
-        </is>
-      </c>
-      <c r="M38" s="14" t="inlineStr">
-        <is>
-          <t>00179038</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L38" s="14" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
       <c r="N38" s="15" t="n">
-        <v>250.5</v>
-      </c>
-      <c r="O38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3462,12 +3462,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3513,16 +3513,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1465.2</v>
+        <v>250.5</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3534,12 +3534,12 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3581,67 +3581,67 @@
         <v>2</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="15" t="n">
-        <v>394</v>
+        <v>1465.2</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
-        <v>131.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -3653,44 +3653,52 @@
         <v>2</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L41" s="11" t="inlineStr"/>
-      <c r="M41" s="11" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L41" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35114</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>00178806</t>
+        </is>
+      </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>0</v>
+        <v>131.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3700,7 +3708,7 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
@@ -3710,29 +3718,21 @@
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34979</t>
-        </is>
-      </c>
-      <c r="M42" s="14" t="inlineStr">
-        <is>
-          <t>00178226</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L42" s="14" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
       <c r="N42" s="15" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="15" t="n">
@@ -3742,32 +3742,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE BAIE-MAHAULT] - Acquisition GEODP Caisse </t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Achat module Caisse </t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3793,19 +3793,19 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>810</v>
+        <v>1100</v>
       </c>
       <c r="O43" s="16" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
@@ -3814,32 +3814,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34925</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
+          <t xml:space="preserve">[COMMUNE DE BAIE-MAHAULT] - Acquisition GEODP Caisse </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>AME multi-communes acheté par la CC</t>
+          <t xml:space="preserve">Achat module Caisse </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3854,30 +3854,30 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34929</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00178034</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>480</v>
+        <v>810</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="P44" s="15" t="n">
         <v>0</v>
@@ -3886,32 +3886,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3921,35 +3921,35 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="12" t="n">
-        <v>362.85</v>
+        <v>480</v>
+      </c>
+      <c r="O45" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
@@ -3958,27 +3958,27 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
@@ -4009,19 +4009,19 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>1073.25</v>
-      </c>
-      <c r="O46" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O46" s="15" t="n">
+        <v>362.85</v>
       </c>
       <c r="P46" s="15" t="n">
         <v>0</v>
@@ -4030,27 +4030,27 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34761</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4081,19 +4081,19 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34768</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00177029</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="12" t="n">
-        <v>781.9</v>
+        <v>1073.25</v>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
@@ -4102,27 +4102,27 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34761</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4153,19 +4153,19 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34768</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00177029</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>2763.25</v>
-      </c>
-      <c r="O48" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>781.9</v>
       </c>
       <c r="P48" s="15" t="n">
         <v>0</v>
@@ -4174,12 +4174,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -4221,37 +4221,37 @@
         <v>3</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>215</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <v>516</v>
+        <v>2763.25</v>
+      </c>
+      <c r="O49" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4293,11 +4293,11 @@
         <v>3</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -4306,44 +4306,44 @@
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>1400</v>
+        <v>516</v>
       </c>
       <c r="P50" s="15" t="n">
-        <v>466.67</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4353,69 +4353,69 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>0</v>
+        <v>466.67</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
@@ -4437,37 +4437,37 @@
         <v>3</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>4.25</v>
+        <v>1.75</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>990</v>
-      </c>
-      <c r="O52" s="16" t="n">
-        <v>585</v>
+        <v>0</v>
+      </c>
+      <c r="O52" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>137.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4497,69 +4497,69 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="12" t="n">
-        <v>910</v>
+        <v>990</v>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>585</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>303.33</v>
+        <v>137.65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4569,69 +4569,69 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>0</v>
+        <v>303.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4641,34 +4641,34 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="O55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4678,27 +4678,27 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4725,20 +4725,20 @@
         <v>4</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>4150</v>
+        <v>153.9</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4750,27 +4750,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
@@ -4790,21 +4790,29 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="L57" s="11" t="inlineStr"/>
-      <c r="M57" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34310</t>
+        </is>
+      </c>
+      <c r="M57" s="11" t="inlineStr">
+        <is>
+          <t>00171605</t>
+        </is>
+      </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="12" t="n">
+        <v>4150</v>
+      </c>
+      <c r="O57" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -4814,27 +4822,27 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4844,7 +4852,7 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">
@@ -4861,22 +4869,14 @@
         <v>4</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M58" s="14" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>7.75</v>
+      </c>
+      <c r="L58" s="14" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
       <c r="N58" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4886,32 +4886,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4921,69 +4921,69 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>1440</v>
+        <v>2500</v>
       </c>
       <c r="O59" s="16" t="n">
-        <v>1152</v>
+        <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
-        <v>62.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -4993,49 +4993,49 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>175</v>
+        <v>1440</v>
       </c>
       <c r="O60" s="16" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="P60" s="15" t="n">
-        <v>0</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -5045,12 +5045,12 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -5077,67 +5077,67 @@
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>775.6</v>
+        <v>175</v>
       </c>
       <c r="O61" s="16" t="n">
-        <v>692.5</v>
+        <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>230.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
@@ -5149,87 +5149,87 @@
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L62" s="14" t="inlineStr"/>
-      <c r="M62" s="14" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L62" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34201</t>
+        </is>
+      </c>
+      <c r="M62" s="14" t="inlineStr">
+        <is>
+          <t>00171162</t>
+        </is>
+      </c>
       <c r="N62" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="15" t="n">
-        <v>0</v>
+        <v>775.6</v>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>692.5</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>0</v>
+        <v>230.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M63" s="11" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr"/>
       <c r="N63" s="12" t="n">
-        <v>5388.936</v>
-      </c>
-      <c r="O63" s="16" t="n">
-        <v>4811.55</v>
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
         <v>0</v>
@@ -5238,27 +5238,27 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
@@ -5289,19 +5289,19 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15" t="n">
-        <v>177.5</v>
+        <v>5388.936</v>
+      </c>
+      <c r="O64" s="16" t="n">
+        <v>4811.55</v>
       </c>
       <c r="P64" s="15" t="n">
         <v>0</v>
@@ -5310,27 +5310,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5361,19 +5361,19 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>1700</v>
-      </c>
-      <c r="O65" s="16" t="n">
-        <v>840</v>
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
+        <v>177.5</v>
       </c>
       <c r="P65" s="12" t="n">
         <v>0</v>
@@ -5382,27 +5382,27 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5417,64 +5417,64 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>1786.1</v>
+        <v>1700</v>
       </c>
       <c r="O66" s="16" t="n">
-        <v>909.9</v>
+        <v>840</v>
       </c>
       <c r="P66" s="15" t="n">
-        <v>303.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5494,64 +5494,64 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>170</v>
+        <v>1786.1</v>
       </c>
       <c r="O67" s="16" t="n">
-        <v>0</v>
+        <v>909.9</v>
       </c>
       <c r="P67" s="12" t="n">
-        <v>0</v>
+        <v>303.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5561,64 +5561,64 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>3000</v>
+        <v>170</v>
       </c>
       <c r="O68" s="16" t="n">
-        <v>1242.9</v>
+        <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>75.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5645,57 +5645,57 @@
         <v>4</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>484</v>
-      </c>
-      <c r="O69" s="12" t="n">
-        <v>572</v>
+        <v>3000</v>
+      </c>
+      <c r="O69" s="16" t="n">
+        <v>1242.9</v>
       </c>
       <c r="P69" s="12" t="n">
-        <v>127.11</v>
+        <v>75.33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5705,64 +5705,64 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="O70" s="16" t="n">
-        <v>0</v>
+        <v>484</v>
+      </c>
+      <c r="O70" s="15" t="n">
+        <v>572</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>0</v>
+        <v>127.11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5793,16 +5793,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5814,32 +5814,32 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5849,34 +5849,34 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
+        <v>170</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5886,27 +5886,27 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5926,44 +5926,44 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>8.25</v>
+        <v>0.75</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O73" s="12" t="n">
-        <v>465.85</v>
+        <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
-        <v>56.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -5998,59 +5998,59 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>3.5</v>
+        <v>8.25</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0</v>
+        <v>465.85</v>
       </c>
       <c r="P74" s="15" t="n">
-        <v>0</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6077,16 +6077,16 @@
         <v>4</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
@@ -6102,32 +6102,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6142,29 +6142,29 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6174,27 +6174,27 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6209,35 +6209,35 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K77" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>2000</v>
+        <v>203.5</v>
       </c>
       <c r="O77" s="16" t="n">
-        <v>1062</v>
+        <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
         <v>0</v>
@@ -6246,27 +6246,27 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6297,19 +6297,19 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>203.5</v>
+        <v>2000</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>0</v>
+        <v>1062</v>
       </c>
       <c r="P78" s="15" t="n">
         <v>0</v>
@@ -6318,27 +6318,27 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6369,19 +6369,19 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>5634.9</v>
+        <v>203.5</v>
       </c>
       <c r="O79" s="16" t="n">
-        <v>2504.4</v>
+        <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
         <v>0</v>
@@ -6390,27 +6390,27 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
@@ -6441,19 +6441,19 @@
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>500</v>
+        <v>5634.9</v>
       </c>
       <c r="O80" s="16" t="n">
-        <v>0</v>
+        <v>2504.4</v>
       </c>
       <c r="P80" s="15" t="n">
         <v>0</v>
@@ -6462,32 +6462,32 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6502,44 +6502,44 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33315</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00167138</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
-        <v>112.38</v>
+        <v>500</v>
+      </c>
+      <c r="O81" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
-        <v>56.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H82" s="14" t="inlineStr">
@@ -6574,61 +6574,69 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L82" s="14" t="inlineStr"/>
-      <c r="M82" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L82" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33315</t>
+        </is>
+      </c>
+      <c r="M82" s="14" t="inlineStr">
+        <is>
+          <t>00167138</t>
+        </is>
+      </c>
       <c r="N82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>0</v>
+        <v>112.38</v>
       </c>
       <c r="P82" s="15" t="n">
-        <v>0</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -6638,29 +6646,21 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33272</t>
-        </is>
-      </c>
-      <c r="M83" s="11" t="inlineStr">
-        <is>
-          <t>00166910</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr"/>
       <c r="N83" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O83" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6670,27 +6670,27 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
@@ -6721,16 +6721,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6742,32 +6742,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6777,38 +6777,38 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>337.5</v>
+        <v>149</v>
       </c>
       <c r="O85" s="16" t="n">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
-        <v>31.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6865,53 +6865,53 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>320</v>
+        <v>337.5</v>
       </c>
       <c r="O86" s="16" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="P86" s="15" t="n">
-        <v>0</v>
+        <v>31.03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6921,35 +6921,35 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="12" t="n">
-        <v>1047</v>
+        <v>320</v>
+      </c>
+      <c r="O87" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
         <v>0</v>
@@ -6958,32 +6958,32 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -6993,35 +6993,35 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0</v>
+        <v>1047</v>
       </c>
       <c r="P88" s="15" t="n">
         <v>0</v>
@@ -7030,32 +7030,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -7077,22 +7077,22 @@
         <v>6</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="O89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7102,32 +7102,32 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -7137,34 +7137,34 @@
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="O90" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7174,32 +7174,32 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -7221,22 +7221,22 @@
         <v>6</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>680.8</v>
-      </c>
-      <c r="O91" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7246,12 +7246,12 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
@@ -7281,32 +7281,32 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>2614.5</v>
+        <v>680.8</v>
       </c>
       <c r="O92" s="16" t="n">
         <v>0</v>
@@ -7318,32 +7318,32 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -7353,34 +7353,34 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
+        <v>2614.5</v>
+      </c>
+      <c r="O93" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7390,32 +7390,32 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
@@ -7437,23 +7437,23 @@
         <v>6</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
         <v>0</v>
@@ -7462,27 +7462,27 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -7497,35 +7497,35 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K95" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>11278.05</v>
-      </c>
-      <c r="O95" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O95" s="12" t="n">
+        <v>276</v>
       </c>
       <c r="P95" s="12" t="n">
         <v>0</v>
@@ -7534,27 +7534,27 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
@@ -7585,16 +7585,16 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>220</v>
+        <v>11278.05</v>
       </c>
       <c r="O96" s="16" t="n">
         <v>0</v>
@@ -7606,12 +7606,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
@@ -7657,16 +7657,16 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="O97" s="16" t="n">
         <v>0</v>
@@ -7678,32 +7678,32 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7713,69 +7713,69 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>318.5</v>
+        <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
-        <v>60.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -7785,64 +7785,64 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>4050</v>
+        <v>910</v>
       </c>
       <c r="O99" s="16" t="n">
-        <v>0</v>
+        <v>318.5</v>
       </c>
       <c r="P99" s="12" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
@@ -7873,16 +7873,16 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>1050</v>
+        <v>4050</v>
       </c>
       <c r="O100" s="16" t="n">
         <v>0</v>
@@ -7894,27 +7894,27 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
@@ -7945,16 +7945,16 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>433.5</v>
+        <v>1050</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7966,32 +7966,32 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -8001,34 +8001,34 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="15" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8038,32 +8038,32 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
@@ -8073,34 +8073,34 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8110,32 +8110,32 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -8150,29 +8150,29 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8182,32 +8182,32 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
@@ -8217,34 +8217,34 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="O105" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8254,27 +8254,27 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -8289,32 +8289,32 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K106" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O106" s="16" t="n">
         <v>0</v>
@@ -8326,27 +8326,27 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
@@ -8377,16 +8377,16 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>130</v>
+        <v>203.5</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8398,12 +8398,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
@@ -8449,16 +8449,16 @@
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O108" s="16" t="n">
         <v>0</v>
@@ -8470,12 +8470,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
@@ -8521,16 +8521,16 @@
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O109" s="16" t="n">
         <v>0</v>
@@ -8542,12 +8542,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F110" s="14" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
@@ -8593,16 +8593,16 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O110" s="16" t="n">
         <v>0</v>
@@ -8614,12 +8614,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -8654,27 +8654,27 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K111" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O111" s="16" t="n">
         <v>0</v>
@@ -8686,32 +8686,32 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
@@ -8721,32 +8721,32 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="O112" s="16" t="n">
         <v>0</v>
@@ -8758,12 +8758,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
@@ -8798,29 +8798,29 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O113" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8830,12 +8830,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
@@ -8902,27 +8902,27 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -8949,16 +8949,16 @@
         <v>9</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>9.25</v>
+        <v>0.5</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
@@ -8974,26 +8974,28 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
@@ -9012,23 +9014,23 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>1</v>
+        <v>9.25</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9044,12 +9046,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9059,13 +9061,11 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v/>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
@@ -9079,34 +9079,34 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>275</v>
-      </c>
-      <c r="O117" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9167,18 +9167,18 @@
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" s="15" t="n">
+        <v>275</v>
+      </c>
+      <c r="O118" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="15" t="n">
@@ -9239,22 +9239,22 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
-        <v>1290</v>
-      </c>
-      <c r="O119" s="16" t="n">
-        <v>895</v>
+        <v>0</v>
+      </c>
+      <c r="O119" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P119" s="12" t="n">
-        <v>526.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -9311,22 +9311,22 @@
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="15" t="n">
-        <v>0</v>
+        <v>1290</v>
+      </c>
+      <c r="O120" s="16" t="n">
+        <v>895</v>
       </c>
       <c r="P120" s="15" t="n">
-        <v>0</v>
+        <v>526.47</v>
       </c>
     </row>
     <row r="121">
@@ -9383,12 +9383,12 @@
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
@@ -9404,12 +9404,12 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
@@ -9419,11 +9419,13 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E122" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
@@ -9442,29 +9444,29 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>4.25</v>
+        <v>1.7</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="15" t="n">
@@ -9474,12 +9476,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9489,7 +9491,7 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9507,32 +9509,32 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.5</v>
+        <v>4.25</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="O123" s="16" t="n">
         <v>0</v>
@@ -9544,28 +9546,26 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E124" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE VILLEJUIF</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="n">
+        <v/>
       </c>
       <c r="F124" s="14" t="inlineStr">
         <is>
@@ -9579,34 +9579,34 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="15" t="n">
+        <v>460</v>
+      </c>
+      <c r="O124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="15" t="n">
@@ -9616,12 +9616,12 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -9631,11 +9631,13 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
@@ -9649,49 +9651,49 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O125" s="16" t="n">
-        <v>2178.28</v>
+        <v>0</v>
+      </c>
+      <c r="O125" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P125" s="12" t="n">
-        <v>207.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9701,7 +9703,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9724,54 +9726,54 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>0.75</v>
+        <v>10.5</v>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="15" t="n">
-        <v>0</v>
+        <v>3016.08</v>
+      </c>
+      <c r="O126" s="16" t="n">
+        <v>2178.28</v>
       </c>
       <c r="P126" s="15" t="n">
-        <v>0</v>
+        <v>207.46</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9789,49 +9791,49 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>10.25</v>
+        <v>0.75</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O127" s="12" t="n">
-        <v>2497.125</v>
+        <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
-        <v>243.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
@@ -9841,7 +9843,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9864,44 +9866,44 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0.5</v>
+        <v>10.25</v>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>0</v>
+        <v>2497.125</v>
       </c>
       <c r="P128" s="15" t="n">
-        <v>0</v>
+        <v>243.62</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9911,7 +9913,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9934,7 +9936,7 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
@@ -9945,12 +9947,12 @@
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
@@ -10015,12 +10017,12 @@
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N130" s="15" t="n">
@@ -10051,7 +10053,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10085,12 +10087,12 @@
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10121,7 +10123,7 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10155,12 +10157,12 @@
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N132" s="15" t="n">
@@ -10176,22 +10178,22 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10209,28 +10211,28 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N133" s="12" t="n">
@@ -10246,12 +10248,12 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22120</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[CD 29 ] FLUX WFS</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
@@ -10261,7 +10263,7 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10274,35 +10276,27 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L134" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M134" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L134" s="14" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
       <c r="N134" s="15" t="n">
         <v>0</v>
       </c>
@@ -10316,22 +10310,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10354,29 +10348,29 @@
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M135" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N135" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="O135" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P135" s="12" t="n">
@@ -10386,12 +10380,12 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
@@ -10401,7 +10395,7 @@
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10424,23 +10418,23 @@
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N136" s="15" t="n">
@@ -10456,22 +10450,22 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10489,34 +10483,34 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K137" s="11" t="n">
         <v>1</v>
       </c>
       <c r="L137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N137" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="O137" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P137" s="12" t="n">
@@ -10526,12 +10520,12 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
@@ -10541,13 +10535,11 @@
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E138" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>SENS</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="n">
+        <v/>
       </c>
       <c r="F138" s="14" t="inlineStr">
         <is>
@@ -10556,27 +10548,35 @@
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L138" s="14" t="inlineStr"/>
-      <c r="M138" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L138" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M138" s="14" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N138" s="15" t="n">
         <v>0</v>
       </c>
@@ -10590,22 +10590,22 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10618,27 +10618,35 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L139" s="11" t="inlineStr"/>
-      <c r="M139" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N139" s="12" t="n">
         <v>0</v>
       </c>
@@ -10652,12 +10660,12 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
@@ -10667,11 +10675,13 @@
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
-        </is>
-      </c>
-      <c r="E140" s="14" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
@@ -10685,19 +10695,19 @@
       </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L140" s="14" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -10714,22 +10724,22 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10737,44 +10747,36 @@
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M141" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr"/>
+      <c r="M141" s="11" t="inlineStr"/>
       <c r="N141" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O141" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P141" s="12" t="n">
@@ -10784,12 +10786,12 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
@@ -10799,7 +10801,7 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10812,35 +10814,27 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M142" s="14" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10854,22 +10848,22 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -10877,36 +10871,44 @@
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr"/>
-      <c r="M143" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N143" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O143" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="12" t="n">
@@ -10916,22 +10918,22 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10944,7 +10946,7 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr">
@@ -10954,17 +10956,25 @@
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L144" s="14" t="inlineStr"/>
-      <c r="M144" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M144" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N144" s="15" t="n">
         <v>0</v>
       </c>
@@ -10978,22 +10988,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11016,14 +11026,14 @@
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -11040,22 +11050,22 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11073,19 +11083,19 @@
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L146" s="14" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -11102,12 +11112,12 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
@@ -11117,7 +11127,7 @@
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11130,7 +11140,7 @@
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
@@ -11140,25 +11150,17 @@
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L147" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M147" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L147" s="11" t="inlineStr"/>
+      <c r="M147" s="11" t="inlineStr"/>
       <c r="N147" s="12" t="n">
         <v>0</v>
       </c>
@@ -11172,22 +11174,22 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
@@ -11203,17 +11205,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H148" s="14" t="inlineStr"/>
+      <c r="H148" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>2.75</v>
+        <v>0.75</v>
       </c>
       <c r="L148" s="14" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -11230,22 +11236,22 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -11258,33 +11264,33 @@
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>8.5</v>
+        <v>1.25</v>
       </c>
       <c r="L149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M149" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N149" s="12" t="n">
@@ -11300,22 +11306,22 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
@@ -11328,31 +11334,23 @@
       </c>
       <c r="G150" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H150" s="14" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L150" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-25456</t>
-        </is>
-      </c>
-      <c r="M150" s="14" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L150" s="14" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
       <c r="N150" s="15" t="n">
         <v>0</v>
       </c>
@@ -11366,24 +11364,26 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C151" s="11" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E151" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="n">
+        <v/>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
@@ -11402,17 +11402,25 @@
       </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L151" s="11" t="inlineStr"/>
-      <c r="M151" s="11" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="L151" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M151" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N151" s="12" t="n">
         <v>0</v>
       </c>
@@ -11426,21 +11434,27 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="C152" s="14" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E152" s="14" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="n">
+        <v/>
+      </c>
       <c r="F152" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11448,23 +11462,31 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr"/>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L152" s="14" t="inlineStr"/>
-      <c r="M152" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L152" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M152" s="14" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N152" s="15" t="n">
         <v>0</v>
       </c>
@@ -11478,46 +11500,58 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PSC-1357</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr"/>
-      <c r="D153" s="11" t="inlineStr"/>
-      <c r="E153" s="11" t="inlineStr"/>
-      <c r="F153" s="11" t="inlineStr"/>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H153" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-36143</t>
-        </is>
-      </c>
+        <v>2.25</v>
+      </c>
+      <c r="L153" s="11" t="inlineStr"/>
       <c r="M153" s="11" t="inlineStr"/>
       <c r="N153" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O153" s="12" t="n">
-        <v>210.8</v>
+        <v>0</v>
       </c>
       <c r="P153" s="12" t="n">
         <v>0</v>
@@ -11526,18 +11560,18 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr"/>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="E154" s="14" t="inlineStr"/>
@@ -11554,11 +11588,11 @@
       <c r="H154" s="14" t="inlineStr"/>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" s="14" t="n">
         <v>0.25</v>
@@ -11578,50 +11612,46 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1357</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr"/>
-      <c r="D155" s="11" t="inlineStr">
-        <is>
-          <t>VILLE DE BARRAUX</t>
-        </is>
-      </c>
+      <c r="D155" s="11" t="inlineStr"/>
       <c r="E155" s="11" t="inlineStr"/>
-      <c r="F155" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+      <c r="F155" s="11" t="inlineStr"/>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr"/>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L155" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L155" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36143</t>
+        </is>
+      </c>
       <c r="M155" s="11" t="inlineStr"/>
       <c r="N155" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O155" s="12" t="n">
-        <v>0</v>
+        <v>210.8</v>
       </c>
       <c r="P155" s="12" t="n">
         <v>0</v>
@@ -11630,18 +11660,18 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C156" s="14" t="inlineStr"/>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E156" s="14" t="inlineStr"/>
@@ -11652,56 +11682,48 @@
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H156" s="14" t="inlineStr"/>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K156" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L156" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M156" s="14" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+      <c r="L156" s="14" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
       <c r="N156" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O156" s="16" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="O156" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P156" s="15" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr"/>
@@ -11718,11 +11740,11 @@
       <c r="H157" s="11" t="inlineStr"/>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K157" s="11" t="n">
         <v>0.25</v>
@@ -11742,18 +11764,18 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
       <c r="D158" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E158" s="14" t="inlineStr"/>
@@ -11770,7 +11792,7 @@
       <c r="H158" s="14" t="inlineStr"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
@@ -11781,39 +11803,39 @@
       </c>
       <c r="L158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34778</t>
+          <t>PDMDEP-35312</t>
         </is>
       </c>
       <c r="M158" s="14" t="inlineStr">
         <is>
-          <t>00172868</t>
+          <t>00177354</t>
         </is>
       </c>
       <c r="N158" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" s="15" t="n">
-        <v>0</v>
+        <v>450</v>
+      </c>
+      <c r="O158" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="P158" s="15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr"/>
@@ -11830,14 +11852,14 @@
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L159" s="11" t="inlineStr"/>
       <c r="M159" s="11" t="inlineStr"/>
@@ -11854,18 +11876,18 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr"/>
@@ -11876,23 +11898,31 @@
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K160" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L160" s="14" t="inlineStr"/>
-      <c r="M160" s="14" t="inlineStr"/>
+      <c r="L160" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M160" s="14" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N160" s="15" t="n">
         <v>0</v>
       </c>
@@ -11906,18 +11936,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -11934,14 +11964,14 @@
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="L161" s="11" t="inlineStr"/>
       <c r="M161" s="11" t="inlineStr"/>
@@ -11958,18 +11988,18 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -11980,31 +12010,23 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K162" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L162" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M162" s="14" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+      <c r="L162" s="14" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
       <c r="N162" s="15" t="n">
         <v>0</v>
       </c>
@@ -12018,18 +12040,18 @@
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12040,31 +12062,23 @@
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L163" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M163" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="L163" s="11" t="inlineStr"/>
+      <c r="M163" s="11" t="inlineStr"/>
       <c r="N163" s="12" t="n">
         <v>0</v>
       </c>
@@ -12078,18 +12092,18 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr"/>
@@ -12100,13 +12114,13 @@
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
@@ -12115,8 +12129,16 @@
       <c r="K164" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L164" s="14" t="inlineStr"/>
-      <c r="M164" s="14" t="inlineStr"/>
+      <c r="L164" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M164" s="14" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N164" s="15" t="n">
         <v>0</v>
       </c>
@@ -12130,18 +12152,18 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1119</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr"/>
@@ -12158,23 +12180,23 @@
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K165" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="L165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30236</t>
+          <t>PDMDEP-33362</t>
         </is>
       </c>
       <c r="M165" s="11" t="inlineStr">
         <is>
-          <t>00152992</t>
+          <t>00167140</t>
         </is>
       </c>
       <c r="N165" s="12" t="n">
@@ -12190,18 +12212,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1060</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12218,11 +12240,11 @@
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K166" s="14" t="n">
         <v>0.25</v>
@@ -12242,18 +12264,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12270,23 +12292,23 @@
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K167" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="L167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26768</t>
+          <t>PDMDEP-30236</t>
         </is>
       </c>
       <c r="M167" s="11" t="inlineStr">
         <is>
-          <t>00141775</t>
+          <t>00152992</t>
         </is>
       </c>
       <c r="N167" s="12" t="n">
@@ -12302,18 +12324,18 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr"/>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr"/>
@@ -12330,14 +12352,14 @@
       <c r="H168" s="14" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J168" s="14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K168" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L168" s="14" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -12352,31 +12374,143 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="17" t="inlineStr">
+      <c r="A169" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C169" s="11" t="inlineStr"/>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="inlineStr"/>
+      <c r="F169" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H169" s="11" t="inlineStr"/>
+      <c r="I169" s="11" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="J169" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K169" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L169" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-26768</t>
+        </is>
+      </c>
+      <c r="M169" s="11" t="inlineStr">
+        <is>
+          <t>00141775</t>
+        </is>
+      </c>
+      <c r="N169" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="13" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B170" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C170" s="14" t="inlineStr"/>
+      <c r="D170" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E170" s="14" t="inlineStr"/>
+      <c r="F170" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G170" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H170" s="14" t="inlineStr"/>
+      <c r="I170" s="14" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="J170" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K170" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L170" s="14" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+      <c r="N170" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B169" s="17" t="inlineStr"/>
-      <c r="C169" s="17" t="inlineStr"/>
-      <c r="D169" s="17" t="inlineStr"/>
-      <c r="E169" s="17" t="inlineStr"/>
-      <c r="F169" s="17" t="inlineStr"/>
-      <c r="G169" s="17" t="inlineStr"/>
-      <c r="H169" s="17" t="inlineStr"/>
-      <c r="I169" s="17" t="inlineStr"/>
-      <c r="J169" s="17" t="inlineStr"/>
-      <c r="K169" s="17" t="inlineStr"/>
-      <c r="L169" s="17" t="inlineStr"/>
-      <c r="M169" s="17" t="inlineStr"/>
-      <c r="N169" s="18" t="n">
+      <c r="B171" s="17" t="inlineStr"/>
+      <c r="C171" s="17" t="inlineStr"/>
+      <c r="D171" s="17" t="inlineStr"/>
+      <c r="E171" s="17" t="inlineStr"/>
+      <c r="F171" s="17" t="inlineStr"/>
+      <c r="G171" s="17" t="inlineStr"/>
+      <c r="H171" s="17" t="inlineStr"/>
+      <c r="I171" s="17" t="inlineStr"/>
+      <c r="J171" s="17" t="inlineStr"/>
+      <c r="K171" s="17" t="inlineStr"/>
+      <c r="L171" s="17" t="inlineStr"/>
+      <c r="M171" s="17" t="inlineStr"/>
+      <c r="N171" s="18" t="n">
         <v>90876.166</v>
       </c>
-      <c r="O169" s="18" t="n">
-        <v>45920.76700000001</v>
-      </c>
-      <c r="P169" s="18" t="n">
-        <v>180.03</v>
+      <c r="O171" s="18" t="n">
+        <v>46010.26700000001</v>
+      </c>
+      <c r="P171" s="18" t="n">
+        <v>178.98</v>
       </c>
     </row>
   </sheetData>
@@ -12546,6 +12680,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13843,16 +13979,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>170</v>
+        <v>171.25</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>21.25</v>
+        <v>21.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>8.83</v>
+        <v>9.33</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>200.08</v>
+        <v>202.08</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>31.75</v>
@@ -13862,7 +13998,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.8%</t>
         </is>
       </c>
     </row>
@@ -13989,16 +14125,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>473898</v>
+        <v>479389</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>196366</v>
+        <v>201946</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>277533</v>
+        <v>277443</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>221195</v>
+        <v>221105</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>13320</v>
@@ -14014,16 +14150,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>255145</v>
+        <v>255056</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>67944</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>187202</v>
+        <v>187112</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>167990</v>
+        <v>167900</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -14039,10 +14175,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>215653</v>
+        <v>221233</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>125322</v>
+        <v>130902</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>90331</v>
@@ -14546,7 +14682,7 @@
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>0</v>
+        <v>895</v>
       </c>
     </row>
     <row r="14">
@@ -14591,7 +14727,7 @@
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>0</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="15">
@@ -14927,7 +15063,7 @@
         </is>
       </c>
       <c r="I22" s="24" t="n">
-        <v>21388</v>
+        <v>26968</v>
       </c>
     </row>
     <row r="23">
@@ -14969,7 +15105,7 @@
         </is>
       </c>
       <c r="I24" s="24" t="n">
-        <v>5785</v>
+        <v>11365</v>
       </c>
     </row>
   </sheetData>
@@ -14983,13 +15119,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -15004,7 +15140,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6 clôture(s) : 6 projet(s), 0 rework</t>
+          <t>7 clôture(s) : 7 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -15221,32 +15357,62 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35840</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE SETE] - Publication des actes</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n">
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-10-21.xlsx
+++ b/jira_export_2026-10-21.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>391 h</t>
+          <t>398 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P174"/>
+  <dimension ref="A1:P175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -2589,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>638.25</v>
       </c>
       <c r="P26" s="15" t="n">
-        <v>638.25</v>
+        <v>425.5</v>
       </c>
     </row>
     <row r="27">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marie-Maud Chiarappa</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -9235,7 +9235,7 @@
         <v>11</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>11</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>11</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>895</v>
       </c>
       <c r="P121" s="12" t="n">
-        <v>526.47</v>
+        <v>471.05</v>
       </c>
     </row>
     <row r="122">
@@ -9451,7 +9451,7 @@
         <v>11</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>11</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>14</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>10.25</v>
+        <v>10.5</v>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>2497.125</v>
       </c>
       <c r="P130" s="15" t="n">
-        <v>243.62</v>
+        <v>237.82</v>
       </c>
     </row>
     <row r="131">
@@ -10664,22 +10664,22 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10692,17 +10692,13 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H140" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr"/>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
@@ -10711,16 +10707,8 @@
       <c r="K140" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L140" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M140" s="14" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+      <c r="L140" s="14" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
       <c r="N140" s="15" t="n">
         <v>0</v>
       </c>
@@ -10734,12 +10722,12 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
@@ -10749,7 +10737,7 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10772,23 +10760,23 @@
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M141" s="11" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N141" s="12" t="n">
@@ -10804,12 +10792,12 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
@@ -10819,13 +10807,11 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E142" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="n">
+        <v/>
       </c>
       <c r="F142" s="14" t="inlineStr">
         <is>
@@ -10834,27 +10820,35 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr"/>
-      <c r="M142" s="14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M142" s="14" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10868,26 +10862,28 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
@@ -10906,14 +10902,14 @@
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="L143" s="11" t="inlineStr"/>
       <c r="M143" s="11" t="inlineStr"/>
@@ -10930,22 +10926,22 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
@@ -10963,7 +10959,7 @@
       </c>
       <c r="H144" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I144" s="14" t="inlineStr">
@@ -10975,7 +10971,7 @@
         <v>22</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L144" s="14" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -10992,22 +10988,22 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -11015,44 +11011,36 @@
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M145" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
       <c r="N145" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O145" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P145" s="12" t="n">
@@ -11062,22 +11050,22 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E146" s="14" t="n">
@@ -11085,7 +11073,7 @@
       </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G146" s="14" t="inlineStr">
@@ -11095,34 +11083,34 @@
       </c>
       <c r="H146" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M146" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N146" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O146" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O146" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P146" s="15" t="n">
@@ -11132,22 +11120,22 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -11160,7 +11148,7 @@
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
@@ -11170,17 +11158,25 @@
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K147" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="L147" s="11" t="inlineStr"/>
-      <c r="M147" s="11" t="inlineStr"/>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N147" s="12" t="n">
         <v>0</v>
       </c>
@@ -11194,12 +11190,12 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr">
@@ -11209,7 +11205,7 @@
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
@@ -11232,14 +11228,14 @@
       </c>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L148" s="14" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -11256,22 +11252,22 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -11294,14 +11290,14 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L149" s="11" t="inlineStr"/>
       <c r="M149" s="11" t="inlineStr"/>
@@ -11318,12 +11314,12 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr">
@@ -11333,7 +11329,7 @@
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E150" s="14" t="n">
@@ -11356,14 +11352,14 @@
       </c>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K150" s="14" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L150" s="14" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -11380,12 +11376,12 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
@@ -11395,7 +11391,7 @@
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -11413,19 +11409,19 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J151" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="L151" s="11" t="inlineStr"/>
       <c r="M151" s="11" t="inlineStr"/>
@@ -11442,12 +11438,12 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B152" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C152" s="14" t="inlineStr">
@@ -11457,7 +11453,7 @@
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E152" s="14" t="n">
@@ -11470,35 +11466,27 @@
       </c>
       <c r="G152" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H152" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J152" s="14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K152" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L152" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M152" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L152" s="14" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
       <c r="N152" s="15" t="n">
         <v>0</v>
       </c>
@@ -11512,22 +11500,22 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -11540,23 +11528,35 @@
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H153" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J153" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L153" s="11" t="inlineStr"/>
-      <c r="M153" s="11" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L153" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N153" s="12" t="n">
         <v>0</v>
       </c>
@@ -11570,12 +11570,12 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C154" s="14" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E154" s="14" t="n">
@@ -11601,32 +11601,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H154" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H154" s="14" t="inlineStr"/>
       <c r="I154" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J154" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K154" s="14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L154" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M154" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>3.75</v>
+      </c>
+      <c r="L154" s="14" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
       <c r="N154" s="15" t="n">
         <v>0</v>
       </c>
@@ -11640,22 +11628,22 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -11668,29 +11656,33 @@
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H155" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J155" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="L155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M155" s="11" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N155" s="12" t="n">
@@ -11706,24 +11698,26 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C156" s="14" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E156" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="n">
+        <v/>
       </c>
       <c r="F156" s="14" t="inlineStr">
         <is>
@@ -11732,27 +11726,31 @@
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H156" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H156" s="14" t="inlineStr"/>
       <c r="I156" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J156" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K156" s="14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L156" s="14" t="inlineStr"/>
-      <c r="M156" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L156" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M156" s="14" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N156" s="15" t="n">
         <v>0</v>
       </c>
@@ -11766,21 +11764,25 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E157" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F157" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11788,20 +11790,24 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H157" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J157" s="11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="L157" s="11" t="inlineStr"/>
       <c r="M157" s="11" t="inlineStr"/>
@@ -11818,46 +11824,50 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>PSC-1357</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr"/>
-      <c r="D158" s="14" t="inlineStr"/>
+      <c r="D158" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE CADENET</t>
+        </is>
+      </c>
       <c r="E158" s="14" t="inlineStr"/>
-      <c r="F158" s="14" t="inlineStr"/>
+      <c r="F158" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H158" s="14" t="inlineStr"/>
       <c r="I158" s="14" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J158" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-36143</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L158" s="14" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
       <c r="N158" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O158" s="15" t="n">
-        <v>210.8</v>
+        <v>0</v>
       </c>
       <c r="P158" s="15" t="n">
         <v>0</v>
@@ -11866,50 +11876,46 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1357</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE BALLAINVILLIERS - FDS</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
-      <c r="D159" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE VALENCAY</t>
-        </is>
-      </c>
+      <c r="D159" s="11" t="inlineStr"/>
       <c r="E159" s="11" t="inlineStr"/>
-      <c r="F159" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+      <c r="F159" s="11" t="inlineStr"/>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr"/>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="J159" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L159" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36143</t>
+        </is>
+      </c>
       <c r="M159" s="11" t="inlineStr"/>
       <c r="N159" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O159" s="12" t="n">
-        <v>0</v>
+        <v>210.8</v>
       </c>
       <c r="P159" s="12" t="n">
         <v>0</v>
@@ -11918,18 +11924,18 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C160" s="14" t="inlineStr"/>
       <c r="D160" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E160" s="14" t="inlineStr"/>
@@ -11946,7 +11952,7 @@
       <c r="H160" s="14" t="inlineStr"/>
       <c r="I160" s="14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J160" s="14" t="n">
@@ -11970,18 +11976,18 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr"/>
@@ -11992,56 +11998,48 @@
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr"/>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J161" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K161" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L161" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M161" s="11" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+      <c r="L161" s="11" t="inlineStr"/>
+      <c r="M161" s="11" t="inlineStr"/>
       <c r="N161" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O161" s="16" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="O161" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="P161" s="12" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C162" s="14" t="inlineStr"/>
       <c r="D162" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E162" s="14" t="inlineStr"/>
@@ -12052,13 +12050,13 @@
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H162" s="14" t="inlineStr"/>
       <c r="I162" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J162" s="14" t="n">
@@ -12067,33 +12065,41 @@
       <c r="K162" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L162" s="14" t="inlineStr"/>
-      <c r="M162" s="14" t="inlineStr"/>
+      <c r="L162" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M162" s="14" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N162" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O162" s="15" t="n">
-        <v>0</v>
+        <v>450</v>
+      </c>
+      <c r="O162" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="P162" s="15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr"/>
@@ -12104,13 +12110,13 @@
       </c>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr"/>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J163" s="11" t="n">
@@ -12119,16 +12125,8 @@
       <c r="K163" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L163" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M163" s="11" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+      <c r="L163" s="11" t="inlineStr"/>
+      <c r="M163" s="11" t="inlineStr"/>
       <c r="N163" s="12" t="n">
         <v>0</v>
       </c>
@@ -12142,18 +12140,18 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C164" s="14" t="inlineStr"/>
       <c r="D164" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E164" s="14" t="inlineStr"/>
@@ -12164,23 +12162,31 @@
       </c>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J164" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K164" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L164" s="14" t="inlineStr"/>
-      <c r="M164" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L164" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M164" s="14" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="N164" s="15" t="n">
         <v>0</v>
       </c>
@@ -12194,18 +12200,18 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr"/>
@@ -12222,14 +12228,14 @@
       <c r="H165" s="11" t="inlineStr"/>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J165" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L165" s="11" t="inlineStr"/>
       <c r="M165" s="11" t="inlineStr"/>
@@ -12246,18 +12252,18 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C166" s="14" t="inlineStr"/>
       <c r="D166" s="14" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E166" s="14" t="inlineStr"/>
@@ -12274,14 +12280,14 @@
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J166" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K166" s="14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="L166" s="14" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -12298,18 +12304,18 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr"/>
@@ -12320,31 +12326,23 @@
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr"/>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J167" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L167" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M167" s="11" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="L167" s="11" t="inlineStr"/>
+      <c r="M167" s="11" t="inlineStr"/>
       <c r="N167" s="12" t="n">
         <v>0</v>
       </c>
@@ -12358,18 +12356,18 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C168" s="14" t="inlineStr"/>
       <c r="D168" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E168" s="14" t="inlineStr"/>
@@ -12386,23 +12384,23 @@
       <c r="H168" s="14" t="inlineStr"/>
       <c r="I168" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J168" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K168" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34335</t>
         </is>
       </c>
       <c r="M168" s="14" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00168072</t>
         </is>
       </c>
       <c r="N168" s="15" t="n">
@@ -12418,18 +12416,18 @@
     <row r="169">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr"/>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr"/>
@@ -12440,23 +12438,31 @@
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr"/>
       <c r="I169" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J169" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L169" s="11" t="inlineStr"/>
-      <c r="M169" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L169" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M169" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N169" s="12" t="n">
         <v>0</v>
       </c>
@@ -12470,18 +12476,18 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>PSC-1119</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C170" s="14" t="inlineStr"/>
       <c r="D170" s="14" t="inlineStr">
         <is>
-          <t>BETSCHDORF</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr"/>
@@ -12492,31 +12498,23 @@
       </c>
       <c r="G170" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H170" s="14" t="inlineStr"/>
       <c r="I170" s="14" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J170" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K170" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L170" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-30236</t>
-        </is>
-      </c>
-      <c r="M170" s="14" t="inlineStr">
-        <is>
-          <t>00152992</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L170" s="14" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
       <c r="N170" s="15" t="n">
         <v>0</v>
       </c>
@@ -12530,18 +12528,18 @@
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>PSC-1060</t>
+          <t>PSC-1119</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr"/>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE COUBLEVIE</t>
+          <t>BETSCHDORF</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr"/>
@@ -12552,23 +12550,31 @@
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr"/>
       <c r="I171" s="11" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="J171" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K171" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L171" s="11" t="inlineStr"/>
-      <c r="M171" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L171" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-30236</t>
+        </is>
+      </c>
+      <c r="M171" s="11" t="inlineStr">
+        <is>
+          <t>00152992</t>
+        </is>
+      </c>
       <c r="N171" s="12" t="n">
         <v>0</v>
       </c>
@@ -12582,18 +12588,18 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1060</t>
         </is>
       </c>
       <c r="B172" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="C172" s="14" t="inlineStr"/>
       <c r="D172" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>MAIRIE DE COUBLEVIE</t>
         </is>
       </c>
       <c r="E172" s="14" t="inlineStr"/>
@@ -12604,31 +12610,23 @@
       </c>
       <c r="G172" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H172" s="14" t="inlineStr"/>
       <c r="I172" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="J172" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K172" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L172" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26768</t>
-        </is>
-      </c>
-      <c r="M172" s="14" t="inlineStr">
-        <is>
-          <t>00141775</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L172" s="14" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
       <c r="N172" s="15" t="n">
         <v>0</v>
       </c>
@@ -12642,18 +12640,18 @@
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1047</t>
         </is>
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr"/>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr"/>
@@ -12664,23 +12662,31 @@
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr"/>
       <c r="I173" s="11" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J173" s="11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K173" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L173" s="11" t="inlineStr"/>
-      <c r="M173" s="11" t="inlineStr"/>
+      <c r="L173" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-26768</t>
+        </is>
+      </c>
+      <c r="M173" s="11" t="inlineStr">
+        <is>
+          <t>00141775</t>
+        </is>
+      </c>
       <c r="N173" s="12" t="n">
         <v>0</v>
       </c>
@@ -12692,31 +12698,83 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="17" t="inlineStr">
+      <c r="A174" s="13" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B174" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C174" s="14" t="inlineStr"/>
+      <c r="D174" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E174" s="14" t="inlineStr"/>
+      <c r="F174" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G174" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H174" s="14" t="inlineStr"/>
+      <c r="I174" s="14" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="J174" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K174" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L174" s="14" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+      <c r="N174" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B174" s="17" t="inlineStr"/>
-      <c r="C174" s="17" t="inlineStr"/>
-      <c r="D174" s="17" t="inlineStr"/>
-      <c r="E174" s="17" t="inlineStr"/>
-      <c r="F174" s="17" t="inlineStr"/>
-      <c r="G174" s="17" t="inlineStr"/>
-      <c r="H174" s="17" t="inlineStr"/>
-      <c r="I174" s="17" t="inlineStr"/>
-      <c r="J174" s="17" t="inlineStr"/>
-      <c r="K174" s="17" t="inlineStr"/>
-      <c r="L174" s="17" t="inlineStr"/>
-      <c r="M174" s="17" t="inlineStr"/>
-      <c r="N174" s="18" t="n">
+      <c r="B175" s="17" t="inlineStr"/>
+      <c r="C175" s="17" t="inlineStr"/>
+      <c r="D175" s="17" t="inlineStr"/>
+      <c r="E175" s="17" t="inlineStr"/>
+      <c r="F175" s="17" t="inlineStr"/>
+      <c r="G175" s="17" t="inlineStr"/>
+      <c r="H175" s="17" t="inlineStr"/>
+      <c r="I175" s="17" t="inlineStr"/>
+      <c r="J175" s="17" t="inlineStr"/>
+      <c r="K175" s="17" t="inlineStr"/>
+      <c r="L175" s="17" t="inlineStr"/>
+      <c r="M175" s="17" t="inlineStr"/>
+      <c r="N175" s="18" t="n">
         <v>90876.166</v>
       </c>
-      <c r="O174" s="18" t="n">
+      <c r="O175" s="18" t="n">
         <v>49557.76700000001</v>
       </c>
-      <c r="P174" s="18" t="n">
-        <v>191.66</v>
+      <c r="P175" s="18" t="n">
+        <v>189.28</v>
       </c>
     </row>
   </sheetData>
@@ -12891,6 +12949,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14188,26 +14247,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>172</v>
+        <v>173.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>22.25</v>
+        <v>23.75</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>9.33</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>203.58</v>
+        <v>206.83</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>31.75</v>
+        <v>32.5</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14308,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>96.58</v>
+        <v>99.33</v>
       </c>
     </row>
   </sheetData>
